--- a/output/pdf_financials_xlsx/BGAU.xlsx
+++ b/output/pdf_financials_xlsx/BGAU.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.003436</v>
+        <v>0.071938</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.001622</v>
+        <v>0.084795</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.003436</v>
+        <v>-0.071938</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.001622</v>
+        <v>-0.084795</v>
       </c>
     </row>
     <row r="12">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
